--- a/mental_health_forms/019_mental_health_support_registration_form--mental_health_forms.xlsx
+++ b/mental_health_forms/019_mental_health_support_registration_form--mental_health_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -531,7 +531,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,13 +571,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email Address</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -600,30 +600,30 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mental_health_counselor</t>
+          <t>date_of_birth</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mental Health Counselor</t>
+          <t>Date of Birth</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,64 +635,64 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>date_of_birth</t>
+          <t>date_of_registration</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Date of Birth</t>
+          <t>Date of Registration</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>date_of_registration</t>
+          <t>time_of_registration</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Date of Registration</t>
+          <t>Time of Registration</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>time_of_registration</t>
+          <t>contact_number</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Time of Registration</t>
+          <t>Contact Number</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,18 +704,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>contact_number</t>
+          <t>address</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Contact Number</t>
+          <t>Address</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,18 +727,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>zip_code</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Address</t>
+          <t>Zip Code</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,18 +750,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>zip_code</t>
+          <t>medical_condition</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Zip Code</t>
+          <t>Medical Condition</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,18 +773,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>medical_condition</t>
+          <t>treatment_goal</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Medical Condition</t>
+          <t>Treatment Goal</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>treatment_goal</t>
+          <t>additional_goal_1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Treatment Goal</t>
+          <t>Additional Question 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>goal</t>
+          <t>additional_goal_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Goal</t>
+          <t>Additional Question 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>goal</t>
+          <t>additional_goal_3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Additional Question 3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,223 +865,16 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>goal</t>
+          <t>additional_goal_4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Additional Question 4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>goal</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>goal</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>goal</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>goal</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>goal</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>goal</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>goal</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>goal</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>goal</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
